--- a/BUT2/Probabilites/Calc.xlsx
+++ b/BUT2/Probabilites/Calc.xlsx
@@ -41,7 +41,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,14 +77,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -377,24 +390,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:E5"/>
+  <dimension ref="A3:E8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="69.140625" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="1" t="e">
         <f>FACT(A4)/FACT(A4-A3)</f>
-        <v>55440</v>
+        <v>#NUM!</v>
       </c>
       <c r="D3" t="s">
         <v>0</v>
@@ -405,23 +418,23 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>11</v>
+        <v>365</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="1" t="e">
         <f>FACT(A4)</f>
-        <v>39916800</v>
+        <v>#NUM!</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="1">
+      <c r="C5" s="2" t="e">
         <f>FACT(A4)/(FACT(A3)*FACT(A4-A3))</f>
-        <v>462</v>
+        <v>#NUM!</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -430,6 +443,7 @@
         <v>6</v>
       </c>
     </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
